--- a/Experiments data/Contraction Limit/Contraction_Limit_Email_Graph.xlsx
+++ b/Experiments data/Contraction Limit/Contraction_Limit_Email_Graph.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fengw\OneDrive\Documents\GitHub\SISR Script\Experiments data\Contraction Limit\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fengw\OneDrive\Documents\GitHub\KaMinPar_Java\Experiments data\Contraction Limit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4798F07F-A932-4293-AC6A-308557BB13E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E02F051-ABA6-416F-9827-29C489435425}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Edge Cuts" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,9 @@
     <sheet name="CCM" sheetId="5" r:id="rId3"/>
     <sheet name="Contiguity" sheetId="7" r:id="rId4"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId5"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="40">
   <si>
     <t>KaHIP</t>
   </si>
@@ -130,6 +133,33 @@
   <si>
     <t>Deep Multilevel, ε= 0</t>
   </si>
+  <si>
+    <t>K = 4, Graph = Email, Contraction = 70%, Cardinality Sizes = [183, 238, 309, 403] at f = 0.3 CL = 170</t>
+  </si>
+  <si>
+    <t>Deep Multilevel, ε = 25</t>
+  </si>
+  <si>
+    <t>Deep Multilevel, ε = 50</t>
+  </si>
+  <si>
+    <t>Deep Multilevel, ε = 100</t>
+  </si>
+  <si>
+    <t>Deep NUGP, ε = 25</t>
+  </si>
+  <si>
+    <t>Deep NUGP, ε = 50</t>
+  </si>
+  <si>
+    <t>Deep NUGP, ε = 100</t>
+  </si>
+  <si>
+    <t>Deep NUGP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edge Cut </t>
+  </si>
 </sst>
 </file>
 
@@ -206,7 +236,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -288,12 +318,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -323,6 +364,7 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -341,13 +383,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -696,7 +747,7 @@
                   <c:v>1526.2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1609.2</c:v>
+                  <c:v>1258.4000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -717,7 +768,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep Multilevel, ε = 5</c:v>
+                  <c:v>Deep Multilevel, ε = 25</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -789,7 +840,7 @@
                   <c:v>1543.2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1549.8</c:v>
+                  <c:v>1254.2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1493,7 +1544,7 @@
                   </a:sysClr>
                 </a:solidFill>
               </a:rPr>
-              <a:t>Edge Cut as Contraction Limit Increases</a:t>
+              <a:t>Edge Cut as Epislon Increases</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1530,12 +1581,13 @@
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="smoothMarker"/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
-          <c:order val="0"/>
+          <c:order val="1"/>
           <c:tx>
             <c:strRef>
               <c:f>'Edge Cuts'!$E$65</c:f>
@@ -1548,162 +1600,100 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
             <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-          </c:marker>
-          <c:xVal>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
             <c:numRef>
-              <c:f>'Edge Cuts'!$D$66:$D$69</c:f>
+              <c:f>'Edge Cuts'!$D$69</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0.15</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.35</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.55000000000000004</c:v>
-                </c:pt>
-                <c:pt idx="3">
                   <c:v>0.7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:xVal>
-          <c:yVal>
+          </c:cat>
+          <c:val>
             <c:numRef>
-              <c:f>'Edge Cuts'!$E$66:$E$69</c:f>
+              <c:f>'Edge Cuts'!$E$69</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>-5.0253573075149729E-2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>-0.11234055632395866</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>-0.12156139542031644</c:v>
-                </c:pt>
-                <c:pt idx="3">
                   <c:v>-0.11065006915629322</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
+          </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-51C4-483C-849D-0D0321525027}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Edge Cuts'!$F$65</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>KaHIP</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'Edge Cuts'!$D$66:$D$69</c:f>
-              <c:numCache>
-                <c:formatCode>0%</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.15</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.35</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.55000000000000004</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.7</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'Edge Cuts'!$F$66:$F$69</c:f>
-              <c:numCache>
-                <c:formatCode>0%</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-51C4-483C-849D-0D0321525027}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1722,72 +1712,97 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:round/>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
             <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent3"/>
-                </a:solidFill>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-          </c:marker>
-          <c:xVal>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
             <c:numRef>
-              <c:f>'Edge Cuts'!$D$66:$D$69</c:f>
+              <c:f>'Edge Cuts'!$D$69</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0.15</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.35</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.55000000000000004</c:v>
-                </c:pt>
-                <c:pt idx="3">
                   <c:v>0.7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:xVal>
-          <c:yVal>
+          </c:cat>
+          <c:val>
             <c:numRef>
-              <c:f>'Edge Cuts'!$G$66:$G$69</c:f>
+              <c:f>'Edge Cuts'!$G$69</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>-0.29322268326417694</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>-8.0528661441524471E-2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>-0.17273705240510215</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>-0.2365145228215767</c:v>
+                  <c:v>3.3041340095282E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
+          </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000002-51C4-483C-849D-0D0321525027}"/>
@@ -1803,102 +1818,489 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep Multilevel, ε = 5</c:v>
+                  <c:v>Deep NUGP, ε = 25</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:round/>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
             <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent4"/>
-                </a:solidFill>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-          </c:marker>
-          <c:xVal>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
             <c:numRef>
-              <c:f>'Edge Cuts'!$D$66:$D$69</c:f>
+              <c:f>'Edge Cuts'!$D$69</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0.15</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.35</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.55000000000000004</c:v>
-                </c:pt>
-                <c:pt idx="3">
                   <c:v>0.7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:xVal>
-          <c:yVal>
+          </c:cat>
+          <c:val>
             <c:numRef>
-              <c:f>'Edge Cuts'!$H$66:$H$69</c:f>
+              <c:f>'Edge Cuts'!$H$69</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>-0.2259105578607653</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>-0.16612878438604564</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>-0.18579990779160899</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>-0.19087136929460569</c:v>
+                  <c:v>3.6268633779007256E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
+          </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000003-51C4-483C-849D-0D0321525027}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Edge Cuts'!$I$65</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Deep NUGP, ε = 50</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent5"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Edge Cuts'!$D$69</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.7</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Edge Cuts'!$I$69</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.11157215306592903</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-DC88-498F-AAE2-9E8EF86BEFA7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Edge Cuts'!$J$65</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Deep NUGP, ε = 100</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent6"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Edge Cuts'!$D$69</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.7</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Edge Cuts'!$J$69</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.12571077301367767</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-DC88-498F-AAE2-9E8EF86BEFA7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
         <c:dLbls>
+          <c:dLblPos val="outEnd"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
+        <c:gapWidth val="150"/>
         <c:axId val="279429695"/>
         <c:axId val="279434975"/>
-      </c:scatterChart>
-      <c:valAx>
+        <c:extLst>
+          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+            <c15:filteredBarSeries>
+              <c15:ser>
+                <c:idx val="1"/>
+                <c:order val="0"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'Edge Cuts'!$F$65</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>KaHIP</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:solidFill>
+                    <a:schemeClr val="accent2"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:invertIfNegative val="0"/>
+                <c:dLbls>
+                  <c:spPr>
+                    <a:noFill/>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                  <c:txPr>
+                    <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                      <a:spAutoFit/>
+                    </a:bodyPr>
+                    <a:lstStyle/>
+                    <a:p>
+                      <a:pPr>
+                        <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                          <a:solidFill>
+                            <a:schemeClr val="tx1">
+                              <a:lumMod val="75000"/>
+                              <a:lumOff val="25000"/>
+                            </a:schemeClr>
+                          </a:solidFill>
+                          <a:latin typeface="+mn-lt"/>
+                          <a:ea typeface="+mn-ea"/>
+                          <a:cs typeface="+mn-cs"/>
+                        </a:defRPr>
+                      </a:pPr>
+                      <a:endParaRPr lang="en-US"/>
+                    </a:p>
+                  </c:txPr>
+                  <c:dLblPos val="outEnd"/>
+                  <c:showLegendKey val="0"/>
+                  <c:showVal val="1"/>
+                  <c:showCatName val="0"/>
+                  <c:showSerName val="0"/>
+                  <c:showPercent val="0"/>
+                  <c:showBubbleSize val="0"/>
+                  <c:showLeaderLines val="0"/>
+                  <c:extLst>
+                    <c:ext uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                      <c15:showLeaderLines val="1"/>
+                      <c15:leaderLines>
+                        <c:spPr>
+                          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                            <a:solidFill>
+                              <a:schemeClr val="tx1">
+                                <a:lumMod val="35000"/>
+                                <a:lumOff val="65000"/>
+                              </a:schemeClr>
+                            </a:solidFill>
+                            <a:round/>
+                          </a:ln>
+                          <a:effectLst/>
+                        </c:spPr>
+                      </c15:leaderLines>
+                    </c:ext>
+                  </c:extLst>
+                </c:dLbls>
+                <c:cat>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'Edge Cuts'!$D$69</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>0%</c:formatCode>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>0.7</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'Edge Cuts'!$F$69</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>0%</c:formatCode>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>0</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000001-51C4-483C-849D-0D0321525027}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredBarSeries>
+          </c:ext>
+        </c:extLst>
+      </c:barChart>
+      <c:catAx>
         <c:axId val="279429695"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
+        <c:delete val="1"/>
+        <c:axPos val="l"/>
         <c:majorGridlines>
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
@@ -1916,7 +2318,7 @@
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
@@ -1955,7 +2357,7 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
@@ -1979,50 +2381,21 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
         <c:crossAx val="279434975"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:tickMarkSkip val="1"/>
+        <c:noMultiLvlLbl val="1"/>
+      </c:catAx>
       <c:valAx>
         <c:axId val="279434975"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
-        <c:axPos val="l"/>
+        <c:axPos val="b"/>
         <c:majorGridlines>
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
@@ -2040,7 +2413,7 @@
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
@@ -2060,7 +2433,7 @@
                   <a:rPr lang="en-US" sz="1800" b="0" i="0" baseline="0">
                     <a:effectLst/>
                   </a:rPr>
-                  <a:t>Percentage of Decline</a:t>
+                  <a:t>Percentage of Improvement</a:t>
                 </a:r>
                 <a:endParaRPr lang="en-US">
                   <a:effectLst/>
@@ -2077,7 +2450,7 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
@@ -2136,7 +2509,7 @@
         </c:txPr>
         <c:crossAx val="279429695"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
+        <c:crossBetween val="between"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -2161,7 +2534,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -2222,6 +2595,1317 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:sysClr>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Observing Edge cut as Epislon varies (email graph)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Edge Cuts'!$B$102</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Deep NUGP</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000009-2C84-42CB-9E97-C0907ABDA5FA}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000008-2C84-42CB-9E97-C0907ABDA5FA}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000007-2C84-42CB-9E97-C0907ABDA5FA}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000006-2C84-42CB-9E97-C0907ABDA5FA}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000005-2C84-42CB-9E97-C0907ABDA5FA}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="5"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000004-2C84-42CB-9E97-C0907ABDA5FA}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="6"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-2C84-42CB-9E97-C0907ABDA5FA}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="7"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000002-2C84-42CB-9E97-C0907ABDA5FA}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="8"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-2C84-42CB-9E97-C0907ABDA5FA}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="9"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-4.5718287102525547E-2"/>
+                  <c:y val="-6.6425916151065592E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{B1F9C556-FC9F-4A21-8747-762203696E82}" type="YVALUE">
+                      <a:rPr lang="en-US" sz="1200"/>
+                      <a:pPr/>
+                      <a:t>[Y VALUE]</a:t>
+                    </a:fld>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="1200"/>
+                      <a:t> </a:t>
+                    </a:r>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                        <a:solidFill>
+                          <a:sysClr val="windowText" lastClr="000000">
+                            <a:lumMod val="75000"/>
+                            <a:lumOff val="25000"/>
+                          </a:sysClr>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>/</a:t>
+                    </a:r>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="1200"/>
+                      <a:t>Unfeasible</a:t>
+                    </a:r>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:showDataLabelsRange val="0"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000A-2C84-42CB-9E97-C0907ABDA5FA}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Edge Cuts'!$A$103:$A$112</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>180</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Edge Cuts'!$B$103:$B$112</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1318</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1319</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1307</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1258</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1159</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1149</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1234</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1341</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1416</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1659</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2C84-42CB-9E97-C0907ABDA5FA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="t"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1153427423"/>
+        <c:axId val="1153432223"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1153427423"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:sysClr>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Epislon Values (Upper Bound = min(Partition size) - 1)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1153432223"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="20"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1153432223"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr algn="ctr">
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:sysClr>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Edge Cut Values (lower is better)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="1.8537794010474583E-2"/>
+              <c:y val="0.1193111386473223"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr">
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1153427423"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="25400">
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:sysClr>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Observing CCM as Epislon Varies (email Graph)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Edge Cuts'!$E$102</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Deep NUGP</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Edge Cuts'!$D$103:$D$112</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>180</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Edge Cuts'!$E$103:$E$112</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.11915269196822E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.14121800529567499</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.17299205648720201</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.229479258605472</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.14121800529567499</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.26301853486319499</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.19947043248014101</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.31950573698146501</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.34950573698146498</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-DE06-45D8-9CAB-5E0FFAD39C44}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="t"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="231460319"/>
+        <c:axId val="231456959"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="231460319"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:sysClr>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Epislon Values (Upper Bound = min(Partition size) - 1)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="231456959"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="20"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="231456959"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:sysClr>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>CCM Values </a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0%" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="231460319"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -3421,7 +5105,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -4127,7 +5811,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -4828,7 +6512,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -6216,6 +7900,86 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -8797,6 +10561,1038 @@
 </file>
 
 <file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -9381,6 +12177,78 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>431427</xdr:colOff>
+      <xdr:row>114</xdr:row>
+      <xdr:rowOff>1121</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2308412</xdr:colOff>
+      <xdr:row>136</xdr:row>
+      <xdr:rowOff>78440</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CE9190D5-A575-BAAD-C24C-3F722BB94254}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>302558</xdr:colOff>
+      <xdr:row>113</xdr:row>
+      <xdr:rowOff>146795</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>582705</xdr:colOff>
+      <xdr:row>136</xdr:row>
+      <xdr:rowOff>33616</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{65C28FE6-339A-4179-15D3-52685DEB9216}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -9590,6 +12458,116 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Edge Cuts"/>
+      <sheetName val="Graph sizes"/>
+      <sheetName val="Runtimes"/>
+      <sheetName val="CCM"/>
+      <sheetName val="Contiguity"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="179">
+          <cell r="B179" t="str">
+            <v>Deep NUGP</v>
+          </cell>
+        </row>
+        <row r="180">
+          <cell r="A180">
+            <v>0</v>
+          </cell>
+          <cell r="B180">
+            <v>458.2</v>
+          </cell>
+        </row>
+        <row r="181">
+          <cell r="A181">
+            <v>280</v>
+          </cell>
+          <cell r="B181">
+            <v>417</v>
+          </cell>
+        </row>
+        <row r="182">
+          <cell r="A182">
+            <v>560</v>
+          </cell>
+          <cell r="B182">
+            <v>385</v>
+          </cell>
+        </row>
+        <row r="183">
+          <cell r="A183">
+            <v>840</v>
+          </cell>
+          <cell r="B183">
+            <v>383</v>
+          </cell>
+        </row>
+        <row r="184">
+          <cell r="A184">
+            <v>1120</v>
+          </cell>
+          <cell r="B184">
+            <v>353</v>
+          </cell>
+        </row>
+        <row r="185">
+          <cell r="A185">
+            <v>1400</v>
+          </cell>
+          <cell r="B185">
+            <v>326</v>
+          </cell>
+        </row>
+        <row r="186">
+          <cell r="A186">
+            <v>1680</v>
+          </cell>
+          <cell r="B186">
+            <v>335</v>
+          </cell>
+        </row>
+        <row r="187">
+          <cell r="A187">
+            <v>1960</v>
+          </cell>
+          <cell r="B187">
+            <v>478</v>
+          </cell>
+        </row>
+        <row r="188">
+          <cell r="A188">
+            <v>2240</v>
+          </cell>
+          <cell r="B188">
+            <v>580</v>
+          </cell>
+        </row>
+        <row r="189">
+          <cell r="A189">
+            <v>2520</v>
+          </cell>
+          <cell r="B189">
+            <v>1150</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9879,7 +12857,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I69"/>
+  <dimension ref="A1:K112"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -9900,26 +12878,26 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
     </row>
     <row r="4" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
@@ -10099,26 +13077,26 @@
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="16" t="s">
+      <c r="A16" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="17"/>
     </row>
     <row r="17" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
@@ -10298,26 +13276,26 @@
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="14" t="s">
+      <c r="A28" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
+      <c r="B28" s="15"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="15"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="15" t="s">
+      <c r="A29" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="B29" s="15"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
+      <c r="B29" s="16"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="16"/>
     </row>
     <row r="30" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="3"/>
@@ -10404,7 +13382,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>12</v>
       </c>
@@ -10433,7 +13411,7 @@
         <v>1650</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>13</v>
       </c>
@@ -10462,7 +13440,7 @@
         <v>1633</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>14</v>
       </c>
@@ -10491,34 +13469,34 @@
         <v>1406</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C40" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" s="15" t="s">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A41" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="B41" s="15"/>
+      <c r="C41" s="15"/>
+      <c r="D41" s="15"/>
+      <c r="E41" s="15"/>
+      <c r="F41" s="15"/>
+      <c r="G41" s="15"/>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A42" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="B42" s="15"/>
-      <c r="C42" s="15"/>
-      <c r="D42" s="15"/>
-      <c r="E42" s="15"/>
-      <c r="F42" s="15"/>
-      <c r="G42" s="15"/>
-    </row>
-    <row r="43" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="B42" s="16"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="16"/>
+      <c r="E42" s="16"/>
+      <c r="F42" s="16"/>
+      <c r="G42" s="16"/>
+    </row>
+    <row r="43" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="3"/>
       <c r="B43" s="1" t="s">
         <v>6</v>
@@ -10542,10 +13520,16 @@
         <v>25</v>
       </c>
       <c r="I43" s="11" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+      <c r="J43" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="K43" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>10</v>
       </c>
@@ -10568,13 +13552,19 @@
         <v>1271</v>
       </c>
       <c r="H44">
-        <v>1657</v>
+        <v>1246</v>
       </c>
       <c r="I44">
-        <v>1402</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+        <v>1321</v>
+      </c>
+      <c r="J44">
+        <v>1086</v>
+      </c>
+      <c r="K44">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>11</v>
       </c>
@@ -10597,13 +13587,19 @@
         <v>1376</v>
       </c>
       <c r="H45">
-        <v>1988</v>
+        <v>1223</v>
       </c>
       <c r="I45">
-        <v>1735</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+        <v>1288</v>
+      </c>
+      <c r="J45">
+        <v>1233</v>
+      </c>
+      <c r="K45">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>12</v>
       </c>
@@ -10626,13 +13622,19 @@
         <v>1302</v>
       </c>
       <c r="H46">
-        <v>1572</v>
+        <v>1230</v>
       </c>
       <c r="I46">
-        <v>1688</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+        <v>1228</v>
+      </c>
+      <c r="J46">
+        <v>1214</v>
+      </c>
+      <c r="K46">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>13</v>
       </c>
@@ -10655,13 +13657,19 @@
         <v>1273</v>
       </c>
       <c r="H47">
-        <v>1413</v>
+        <v>1345</v>
       </c>
       <c r="I47">
-        <v>1511</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+        <v>1202</v>
+      </c>
+      <c r="J47">
+        <v>1121</v>
+      </c>
+      <c r="K47">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>14</v>
       </c>
@@ -10684,24 +13692,30 @@
         <v>1285</v>
       </c>
       <c r="H48">
-        <v>1416</v>
+        <v>1248</v>
       </c>
       <c r="I48">
-        <v>1413</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A52" s="13" t="s">
+        <v>1232</v>
+      </c>
+      <c r="J48">
+        <v>1127</v>
+      </c>
+      <c r="K48">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A52" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="B52" s="13"/>
-      <c r="C52" s="13"/>
-      <c r="D52" s="13"/>
-      <c r="E52" s="13"/>
-      <c r="F52" s="13"/>
-      <c r="G52" s="13"/>
-    </row>
-    <row r="53" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="B52" s="14"/>
+      <c r="C52" s="14"/>
+      <c r="D52" s="14"/>
+      <c r="E52" s="14"/>
+      <c r="F52" s="14"/>
+      <c r="G52" s="14"/>
+    </row>
+    <row r="53" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A53" s="3"/>
       <c r="B53" s="1" t="s">
         <v>6</v>
@@ -10725,10 +13739,16 @@
         <v>30</v>
       </c>
       <c r="I53" s="11" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+      <c r="J53" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="K53" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="8">
         <v>0.15</v>
       </c>
@@ -10765,7 +13785,7 @@
         <v>1595.4</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="9">
         <v>0.35</v>
       </c>
@@ -10802,7 +13822,7 @@
         <v>1517.6</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="9">
         <v>0.55000000000000004</v>
       </c>
@@ -10839,7 +13859,7 @@
         <v>1543.2</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="9">
         <v>0.7</v>
       </c>
@@ -10869,14 +13889,22 @@
       </c>
       <c r="H57">
         <f>AVERAGE(H44:H48)</f>
-        <v>1609.2</v>
+        <v>1258.4000000000001</v>
       </c>
       <c r="I57">
         <f>AVERAGE(I44:I48)</f>
-        <v>1549.8</v>
-      </c>
-    </row>
-    <row r="65" spans="4:8" x14ac:dyDescent="0.25">
+        <v>1254.2</v>
+      </c>
+      <c r="J57">
+        <f>AVERAGE(J44:J48)</f>
+        <v>1156.2</v>
+      </c>
+      <c r="K57">
+        <f>AVERAGE(K44:K48)</f>
+        <v>1137.8</v>
+      </c>
+    </row>
+    <row r="65" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D65" s="3"/>
       <c r="E65" s="1" t="s">
         <v>1</v>
@@ -10888,91 +13916,263 @@
         <v>30</v>
       </c>
       <c r="H65" s="11" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="66" spans="4:8" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+      <c r="I65" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="J65" s="11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="66" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D66" s="8">
         <v>0.15</v>
       </c>
-      <c r="E66" s="21">
+      <c r="E66" s="13">
         <f>(G54 - F54) / G54</f>
         <v>-5.0253573075149729E-2</v>
       </c>
-      <c r="F66" s="21">
+      <c r="F66" s="13">
         <f>(G54 - G54) / G54</f>
         <v>0</v>
       </c>
-      <c r="G66" s="21">
+      <c r="G66" s="13">
         <f>(G54 - H54) / G54</f>
         <v>-0.29322268326417694</v>
       </c>
-      <c r="H66" s="21">
+      <c r="H66" s="13">
         <f>(G54 - I54) / G54</f>
         <v>-0.2259105578607653</v>
       </c>
     </row>
-    <row r="67" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D67" s="9">
         <v>0.35</v>
       </c>
-      <c r="E67" s="21">
+      <c r="E67" s="13">
         <f t="shared" ref="E67:E69" si="4">(G55 - F55) / G55</f>
         <v>-0.11234055632395866</v>
       </c>
-      <c r="F67" s="21">
+      <c r="F67" s="13">
         <f t="shared" ref="F67:F69" si="5">(G55 - G55) / G55</f>
         <v>0</v>
       </c>
-      <c r="G67" s="21">
+      <c r="G67" s="13">
         <f t="shared" ref="G67:G69" si="6">(G55 - H55) / G55</f>
         <v>-8.0528661441524471E-2</v>
       </c>
-      <c r="H67" s="21">
-        <f t="shared" ref="H67:H69" si="7">(G55 - I55) / G55</f>
+      <c r="H67" s="13">
+        <f t="shared" ref="H67:H68" si="7">(G55 - I55) / G55</f>
         <v>-0.16612878438604564</v>
       </c>
     </row>
-    <row r="68" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D68" s="9">
         <v>0.55000000000000004</v>
       </c>
-      <c r="E68" s="21">
+      <c r="E68" s="13">
         <f t="shared" si="4"/>
         <v>-0.12156139542031644</v>
       </c>
-      <c r="F68" s="21">
+      <c r="F68" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G68" s="21">
+      <c r="G68" s="13">
         <f t="shared" si="6"/>
         <v>-0.17273705240510215</v>
       </c>
-      <c r="H68" s="21">
+      <c r="H68" s="13">
         <f t="shared" si="7"/>
         <v>-0.18579990779160899</v>
       </c>
     </row>
-    <row r="69" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D69" s="9">
         <v>0.7</v>
       </c>
-      <c r="E69" s="21">
+      <c r="E69" s="13">
         <f t="shared" si="4"/>
         <v>-0.11065006915629322</v>
       </c>
-      <c r="F69" s="21">
+      <c r="F69" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G69" s="21">
+      <c r="G69" s="13">
         <f t="shared" si="6"/>
-        <v>-0.2365145228215767</v>
-      </c>
-      <c r="H69" s="21">
-        <f t="shared" si="7"/>
-        <v>-0.19087136929460569</v>
+        <v>3.3041340095282E-2</v>
+      </c>
+      <c r="H69" s="13">
+        <f>(G57 - I57) / G57</f>
+        <v>3.6268633779007256E-2</v>
+      </c>
+      <c r="I69" s="13">
+        <f>(G57 - J57) / G57</f>
+        <v>0.11157215306592903</v>
+      </c>
+      <c r="J69" s="13">
+        <f>(G57 - K57) / G57</f>
+        <v>0.12571077301367767</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B101" t="s">
+        <v>39</v>
+      </c>
+      <c r="D101" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" s="22"/>
+      <c r="B102" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D102" s="22"/>
+      <c r="E102" s="11" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" s="10">
+        <v>0</v>
+      </c>
+      <c r="B103" s="22">
+        <v>1318</v>
+      </c>
+      <c r="D103" s="10">
+        <v>0</v>
+      </c>
+      <c r="E103" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" s="10">
+        <v>20</v>
+      </c>
+      <c r="B104" s="22">
+        <v>1319</v>
+      </c>
+      <c r="D104" s="10">
+        <v>20</v>
+      </c>
+      <c r="E104" s="2">
+        <v>5.11915269196822E-2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" s="10">
+        <v>40</v>
+      </c>
+      <c r="B105" s="23">
+        <v>1307</v>
+      </c>
+      <c r="D105" s="10">
+        <v>40</v>
+      </c>
+      <c r="E105" s="2">
+        <v>0.14121800529567499</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" s="10">
+        <v>60</v>
+      </c>
+      <c r="B106" s="23">
+        <v>1258</v>
+      </c>
+      <c r="D106" s="10">
+        <v>60</v>
+      </c>
+      <c r="E106" s="2">
+        <v>0.17299205648720201</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" s="10">
+        <v>80</v>
+      </c>
+      <c r="B107" s="22">
+        <v>1159</v>
+      </c>
+      <c r="D107" s="10">
+        <v>80</v>
+      </c>
+      <c r="E107" s="2">
+        <v>0.229479258605472</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" s="24">
+        <v>100</v>
+      </c>
+      <c r="B108" s="22">
+        <v>1149</v>
+      </c>
+      <c r="D108" s="24">
+        <v>100</v>
+      </c>
+      <c r="E108" s="2">
+        <v>0.14121800529567499</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" s="24">
+        <v>120</v>
+      </c>
+      <c r="B109" s="22">
+        <v>1234</v>
+      </c>
+      <c r="D109" s="24">
+        <v>120</v>
+      </c>
+      <c r="E109" s="12">
+        <v>0.26301853486319499</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" s="24">
+        <v>140</v>
+      </c>
+      <c r="B110" s="22">
+        <v>1341</v>
+      </c>
+      <c r="D110" s="24">
+        <v>140</v>
+      </c>
+      <c r="E110" s="12">
+        <v>0.19947043248014101</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" s="25">
+        <v>160</v>
+      </c>
+      <c r="B111" s="22">
+        <v>1416</v>
+      </c>
+      <c r="D111" s="25">
+        <v>160</v>
+      </c>
+      <c r="E111" s="2">
+        <v>0.31950573698146501</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" s="25">
+        <v>180</v>
+      </c>
+      <c r="B112" s="22">
+        <v>1659</v>
+      </c>
+      <c r="D112" s="25">
+        <v>180</v>
+      </c>
+      <c r="E112" s="2">
+        <v>0.34950573698146498</v>
       </c>
     </row>
   </sheetData>
@@ -11006,26 +14206,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="18"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="19"/>
     </row>
     <row r="3" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
@@ -11200,26 +14400,26 @@
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="14" t="s">
+      <c r="A13" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="18"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="19"/>
     </row>
     <row r="15" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
@@ -11394,26 +14594,26 @@
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="14" t="s">
+      <c r="A24" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
+      <c r="B24" s="15"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="15"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="17" t="s">
+      <c r="A25" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="18"/>
+      <c r="B25" s="17"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="19"/>
     </row>
     <row r="26" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A26" s="5"/>
@@ -11588,26 +14788,26 @@
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="14" t="s">
+      <c r="A35" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
+      <c r="B35" s="15"/>
+      <c r="C35" s="15"/>
+      <c r="D35" s="15"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="15"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="17" t="s">
+      <c r="A36" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="B36" s="16"/>
-      <c r="C36" s="16"/>
-      <c r="D36" s="16"/>
-      <c r="E36" s="16"/>
-      <c r="F36" s="16"/>
-      <c r="G36" s="18"/>
+      <c r="B36" s="17"/>
+      <c r="C36" s="17"/>
+      <c r="D36" s="17"/>
+      <c r="E36" s="17"/>
+      <c r="F36" s="17"/>
+      <c r="G36" s="19"/>
     </row>
     <row r="37" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A37" s="5"/>
@@ -11782,15 +14982,15 @@
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A49" s="13" t="s">
+      <c r="A49" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="B49" s="13"/>
-      <c r="C49" s="13"/>
-      <c r="D49" s="13"/>
-      <c r="E49" s="13"/>
-      <c r="F49" s="13"/>
-      <c r="G49" s="13"/>
+      <c r="B49" s="14"/>
+      <c r="C49" s="14"/>
+      <c r="D49" s="14"/>
+      <c r="E49" s="14"/>
+      <c r="F49" s="14"/>
+      <c r="G49" s="14"/>
     </row>
     <row r="50" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A50" s="3"/>
@@ -12011,15 +15211,15 @@
       <c r="G1" s="20"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
     </row>
     <row r="3" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
@@ -12167,11 +15367,11 @@
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
@@ -12273,26 +15473,26 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="14" t="s">
+      <c r="A21" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="15" t="s">
+      <c r="A22" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B22" s="15"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
+      <c r="B22" s="16"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
     </row>
     <row r="23" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
@@ -12437,11 +15637,11 @@
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="19" t="s">
+      <c r="A30" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
+      <c r="B30" s="21"/>
+      <c r="C30" s="21"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B31" s="1" t="s">
@@ -12543,26 +15743,26 @@
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" s="14" t="s">
+      <c r="A40" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
+      <c r="B40" s="15"/>
+      <c r="C40" s="15"/>
+      <c r="D40" s="15"/>
+      <c r="E40" s="15"/>
+      <c r="F40" s="15"/>
+      <c r="G40" s="15"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="15" t="s">
+      <c r="A41" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B41" s="15"/>
-      <c r="C41" s="15"/>
-      <c r="D41" s="15"/>
-      <c r="E41" s="15"/>
-      <c r="F41" s="15"/>
-      <c r="G41" s="15"/>
+      <c r="B41" s="16"/>
+      <c r="C41" s="16"/>
+      <c r="D41" s="16"/>
+      <c r="E41" s="16"/>
+      <c r="F41" s="16"/>
+      <c r="G41" s="16"/>
     </row>
     <row r="42" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A42" s="3"/>
@@ -12707,11 +15907,11 @@
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A49" s="19" t="s">
+      <c r="A49" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B49" s="19"/>
-      <c r="C49" s="19"/>
+      <c r="B49" s="21"/>
+      <c r="C49" s="21"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B50" s="1" t="s">
@@ -12813,26 +16013,26 @@
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A59" s="14" t="s">
+      <c r="A59" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="B59" s="14"/>
-      <c r="C59" s="14"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="14"/>
-      <c r="G59" s="14"/>
+      <c r="B59" s="15"/>
+      <c r="C59" s="15"/>
+      <c r="D59" s="15"/>
+      <c r="E59" s="15"/>
+      <c r="F59" s="15"/>
+      <c r="G59" s="15"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" s="15" t="s">
+      <c r="A60" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B60" s="15"/>
-      <c r="C60" s="15"/>
-      <c r="D60" s="15"/>
-      <c r="E60" s="15"/>
-      <c r="F60" s="15"/>
-      <c r="G60" s="15"/>
+      <c r="B60" s="16"/>
+      <c r="C60" s="16"/>
+      <c r="D60" s="16"/>
+      <c r="E60" s="16"/>
+      <c r="F60" s="16"/>
+      <c r="G60" s="16"/>
     </row>
     <row r="61" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A61" s="3"/>
@@ -12947,11 +16147,11 @@
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A68" s="19" t="s">
+      <c r="A68" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B68" s="19"/>
-      <c r="C68" s="19"/>
+      <c r="B68" s="21"/>
+      <c r="C68" s="21"/>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B69" s="1" t="s">
@@ -13053,26 +16253,26 @@
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A78" s="13" t="s">
+      <c r="A78" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="B78" s="13"/>
-      <c r="C78" s="13"/>
-      <c r="D78" s="13"/>
-      <c r="E78" s="13"/>
-      <c r="F78" s="13"/>
-      <c r="G78" s="13"/>
+      <c r="B78" s="14"/>
+      <c r="C78" s="14"/>
+      <c r="D78" s="14"/>
+      <c r="E78" s="14"/>
+      <c r="F78" s="14"/>
+      <c r="G78" s="14"/>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A79" s="15" t="s">
+      <c r="A79" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B79" s="15"/>
-      <c r="C79" s="15"/>
-      <c r="D79" s="15"/>
-      <c r="E79" s="15"/>
-      <c r="F79" s="15"/>
-      <c r="G79" s="15"/>
+      <c r="B79" s="16"/>
+      <c r="C79" s="16"/>
+      <c r="D79" s="16"/>
+      <c r="E79" s="16"/>
+      <c r="F79" s="16"/>
+      <c r="G79" s="16"/>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="6"/>
@@ -13093,19 +16293,19 @@
       <c r="A81" s="7">
         <v>0.15</v>
       </c>
-      <c r="B81" s="21">
+      <c r="B81" s="13">
         <f>AVERAGE(F4:F8)</f>
         <v>0.25680000000000003</v>
       </c>
-      <c r="C81" s="21">
+      <c r="C81" s="13">
         <f>AVERAGE(G4:G8)</f>
         <v>0.27698</v>
       </c>
-      <c r="D81" s="21">
+      <c r="D81" s="13">
         <f>AVERAGE(H4:H8)</f>
         <v>0</v>
       </c>
-      <c r="E81" s="21">
+      <c r="E81" s="13">
         <f>AVERAGE(I4:I8)</f>
         <v>2.5231200000000002E-2</v>
       </c>
@@ -13114,19 +16314,19 @@
       <c r="A82" s="7">
         <v>0.35</v>
       </c>
-      <c r="B82" s="21">
+      <c r="B82" s="13">
         <f>AVERAGE(F24:F28)</f>
         <v>0.25919999999999999</v>
       </c>
-      <c r="C82" s="21">
+      <c r="C82" s="13">
         <f>AVERAGE(G24:G28)</f>
         <v>0.27698</v>
       </c>
-      <c r="D82" s="21">
+      <c r="D82" s="13">
         <f>AVERAGE(H24:H28)</f>
         <v>0</v>
       </c>
-      <c r="E82" s="21">
+      <c r="E82" s="13">
         <f>AVERAGE(I24:I28)</f>
         <v>3.3140000000000003E-2</v>
       </c>
@@ -13135,19 +16335,19 @@
       <c r="A83" s="7">
         <v>0.55000000000000004</v>
       </c>
-      <c r="B83" s="21">
+      <c r="B83" s="13">
         <f>AVERAGE(F43:F47)</f>
         <v>0.25759999999999994</v>
       </c>
-      <c r="C83" s="21">
+      <c r="C83" s="13">
         <f>AVERAGE(G43:G47)</f>
         <v>0.27698</v>
       </c>
-      <c r="D83" s="21">
+      <c r="D83" s="13">
         <f>AVERAGE(H43:H47)</f>
         <v>0</v>
       </c>
-      <c r="E83" s="21">
+      <c r="E83" s="13">
         <f>AVERAGE(I43:I47)</f>
         <v>3.2440000000000004E-2</v>
       </c>
@@ -13156,32 +16356,32 @@
       <c r="A84" s="7">
         <v>0.7</v>
       </c>
-      <c r="B84" s="21">
+      <c r="B84" s="13">
         <f>AVERAGE(F62:F66)</f>
         <v>0.25944</v>
       </c>
-      <c r="C84" s="21">
+      <c r="C84" s="13">
         <f>AVERAGE(G62:G66)</f>
         <v>0.27698</v>
       </c>
-      <c r="D84" s="21">
+      <c r="D84" s="13">
         <f>AVERAGE(H62:H66)</f>
         <v>0</v>
       </c>
-      <c r="E84" s="21">
+      <c r="E84" s="13">
         <f>AVERAGE(I62:I66)</f>
         <v>1.3763999999999998E-2</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D85" s="21"/>
+      <c r="D85" s="13"/>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90" s="19" t="s">
+      <c r="A90" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B90" s="19"/>
-      <c r="C90" s="19"/>
+      <c r="B90" s="21"/>
+      <c r="C90" s="21"/>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B91" s="1" t="s">
@@ -13279,21 +16479,21 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A60:G60"/>
+    <mergeCell ref="A68:C68"/>
+    <mergeCell ref="A78:G78"/>
+    <mergeCell ref="A79:G79"/>
+    <mergeCell ref="A90:C90"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A59:G59"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A10:C10"/>
     <mergeCell ref="A21:G21"/>
     <mergeCell ref="A22:G22"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A40:G40"/>
-    <mergeCell ref="A41:G41"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A59:G59"/>
-    <mergeCell ref="A60:G60"/>
-    <mergeCell ref="A68:C68"/>
-    <mergeCell ref="A78:G78"/>
-    <mergeCell ref="A79:G79"/>
-    <mergeCell ref="A90:C90"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13327,15 +16527,15 @@
       <c r="G1" s="20"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="18"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="19"/>
     </row>
     <row r="3" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
@@ -13510,26 +16710,26 @@
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="14" t="s">
+      <c r="A13" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="18"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="19"/>
     </row>
     <row r="15" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
@@ -13704,26 +16904,26 @@
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="14" t="s">
+      <c r="A24" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
+      <c r="B24" s="15"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="15"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="17" t="s">
+      <c r="A25" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="18"/>
+      <c r="B25" s="17"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="19"/>
     </row>
     <row r="26" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A26" s="5"/>
@@ -13898,26 +17098,26 @@
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="14" t="s">
+      <c r="A36" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
+      <c r="B36" s="15"/>
+      <c r="C36" s="15"/>
+      <c r="D36" s="15"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="15"/>
+      <c r="G36" s="15"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="17" t="s">
+      <c r="A37" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="B37" s="16"/>
-      <c r="C37" s="16"/>
-      <c r="D37" s="16"/>
-      <c r="E37" s="16"/>
-      <c r="F37" s="16"/>
-      <c r="G37" s="18"/>
+      <c r="B37" s="17"/>
+      <c r="C37" s="17"/>
+      <c r="D37" s="17"/>
+      <c r="E37" s="17"/>
+      <c r="F37" s="17"/>
+      <c r="G37" s="19"/>
     </row>
     <row r="38" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A38" s="5"/>
@@ -14092,26 +17292,26 @@
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A59" s="13" t="s">
+      <c r="A59" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="B59" s="13"/>
-      <c r="C59" s="13"/>
-      <c r="D59" s="13"/>
-      <c r="E59" s="13"/>
-      <c r="F59" s="13"/>
-      <c r="G59" s="13"/>
+      <c r="B59" s="14"/>
+      <c r="C59" s="14"/>
+      <c r="D59" s="14"/>
+      <c r="E59" s="14"/>
+      <c r="F59" s="14"/>
+      <c r="G59" s="14"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" s="17" t="s">
+      <c r="A60" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="B60" s="16"/>
-      <c r="C60" s="16"/>
-      <c r="D60" s="16"/>
-      <c r="E60" s="16"/>
-      <c r="F60" s="16"/>
-      <c r="G60" s="18"/>
+      <c r="B60" s="17"/>
+      <c r="C60" s="17"/>
+      <c r="D60" s="17"/>
+      <c r="E60" s="17"/>
+      <c r="F60" s="17"/>
+      <c r="G60" s="19"/>
     </row>
     <row r="61" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A61" s="6"/>
